--- a/web/public/templates/Team-Setup-Template.xlsx
+++ b/web/public/templates/Team-Setup-Template.xlsx
@@ -19,13 +19,13 @@
   <definedNames>
     <definedName name="YesNo">Choices!$A$2:$A$3</definedName>
     <definedName name="Days">Choices!$B$2:$B$8</definedName>
-    <definedName name="EventTypes">Choices!$C$2:$C$4</definedName>
+    <definedName name="EventTypes">Choices!$C$2:$C$5</definedName>
     <definedName name="Repeats">Choices!$D$2:$D$5</definedName>
     <definedName name="Shirts">Choices!$E$2:$E$11</definedName>
     <definedName name="RefGroups">Choices!$F$2:$F$3</definedName>
-    <definedName name="Lists">Choices!$G$2:$G$3</definedName>
+    <definedName name="Lists">Choices!$G$2:$G$4</definedName>
     <definedName name="Programs">Choices!$H$2:$H$4</definedName>
-    <definedName name="DefaultKinds">Choices!$I$2:$I$4</definedName>
+    <definedName name="DefaultKinds">Choices!$I$2:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Team'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Staff'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Roster'!$1:$1</definedName>
@@ -371,6 +371,21 @@
         <t>Blank = end of the season (June 30).</t>
       </text>
     </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Blank = weekly. Or Every 2 weeks, Every 3 weeks, or None for this one date only.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Like 3, or Courts 3-4.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Practice uniform color. New colors are added to the team's list.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -403,12 +418,22 @@
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>For team events only; tournaments don't repeat.</t>
+        <t>For practices and team events; tournaments don't repeat.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Days of the week, like 'Tue, Thu'.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Practices only.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Practices only.</t>
       </text>
     </comment>
   </commentList>
@@ -885,7 +910,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>One row per weekly practice.</t>
+          <t>One row per practice series: weekly, every 2 weeks or every 3 weeks.</t>
         </is>
       </c>
       <c r="C17" s="6">
@@ -901,7 +926,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>One row per tournament, team event or deadline.</t>
+          <t>One row per tournament, team event, deadline or one-off practice.</t>
         </is>
       </c>
       <c r="C18" s="6">
@@ -917,7 +942,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Optional: packing checklist and uniform items.</t>
+          <t>Optional: packing checklist, uniform items and practice uniform colors.</t>
         </is>
       </c>
       <c r="C19" s="6">
@@ -9135,7 +9160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9144,8 +9169,11 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -9181,10 +9209,25 @@
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
+          <t>Repeats</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Uniform color</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -9219,10 +9262,25 @@
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
           <t>A5 Sportsplex</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>Bring both jerseys</t>
         </is>
@@ -9237,6 +9295,9 @@
       <c r="F3" s="15" t="n"/>
       <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -9247,6 +9308,9 @@
       <c r="F4" s="15" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -9257,6 +9321,9 @@
       <c r="F5" s="15" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -9267,6 +9334,9 @@
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -9277,6 +9347,9 @@
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -9287,6 +9360,9 @@
       <c r="F8" s="15" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -9297,6 +9373,9 @@
       <c r="F9" s="15" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -9307,6 +9386,9 @@
       <c r="F10" s="15" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -9317,6 +9399,9 @@
       <c r="F11" s="15" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -9327,6 +9412,9 @@
       <c r="F12" s="15" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -9337,6 +9425,9 @@
       <c r="F13" s="15" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -9347,6 +9438,9 @@
       <c r="F14" s="15" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -9357,6 +9451,9 @@
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -9367,6 +9464,9 @@
       <c r="F16" s="15" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9377,6 +9477,9 @@
       <c r="F17" s="15" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -9387,6 +9490,9 @@
       <c r="F18" s="15" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -9397,6 +9503,9 @@
       <c r="F19" s="15" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -9407,6 +9516,9 @@
       <c r="F20" s="15" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9417,6 +9529,9 @@
       <c r="F21" s="15" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -9427,6 +9542,9 @@
       <c r="F22" s="15" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -9437,6 +9555,9 @@
       <c r="F23" s="15" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -9447,6 +9568,9 @@
       <c r="F24" s="15" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -9457,6 +9581,9 @@
       <c r="F25" s="15" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -9467,6 +9594,9 @@
       <c r="F26" s="15" t="n"/>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -9477,6 +9607,9 @@
       <c r="F27" s="15" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -9487,6 +9620,9 @@
       <c r="F28" s="15" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -9497,6 +9633,9 @@
       <c r="F29" s="15" t="n"/>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -9507,6 +9646,9 @@
       <c r="F30" s="15" t="n"/>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -9517,6 +9659,9 @@
       <c r="F31" s="15" t="n"/>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -9527,6 +9672,9 @@
       <c r="F32" s="15" t="n"/>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -9537,6 +9685,9 @@
       <c r="F33" s="15" t="n"/>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -9547,6 +9698,9 @@
       <c r="F34" s="15" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -9557,6 +9711,9 @@
       <c r="F35" s="15" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -9567,6 +9724,9 @@
       <c r="F36" s="15" t="n"/>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -9577,6 +9737,9 @@
       <c r="F37" s="15" t="n"/>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -9587,6 +9750,9 @@
       <c r="F38" s="15" t="n"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -9597,6 +9763,9 @@
       <c r="F39" s="15" t="n"/>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -9607,6 +9776,9 @@
       <c r="F40" s="15" t="n"/>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -9617,6 +9789,9 @@
       <c r="F41" s="15" t="n"/>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -9627,6 +9802,9 @@
       <c r="F42" s="15" t="n"/>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -9637,6 +9815,9 @@
       <c r="F43" s="15" t="n"/>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -9647,6 +9828,9 @@
       <c r="F44" s="15" t="n"/>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -9657,6 +9841,9 @@
       <c r="F45" s="15" t="n"/>
       <c r="G45" s="6" t="n"/>
       <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -9667,6 +9854,9 @@
       <c r="F46" s="15" t="n"/>
       <c r="G46" s="6" t="n"/>
       <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -9677,6 +9867,9 @@
       <c r="F47" s="15" t="n"/>
       <c r="G47" s="6" t="n"/>
       <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n"/>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -9687,6 +9880,9 @@
       <c r="F48" s="15" t="n"/>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="6" t="n"/>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -9697,6 +9893,9 @@
       <c r="F49" s="15" t="n"/>
       <c r="G49" s="6" t="n"/>
       <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -9707,6 +9906,9 @@
       <c r="F50" s="15" t="n"/>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -9717,6 +9919,9 @@
       <c r="F51" s="15" t="n"/>
       <c r="G51" s="6" t="n"/>
       <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -9727,6 +9932,9 @@
       <c r="F52" s="15" t="n"/>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -9737,6 +9945,9 @@
       <c r="F53" s="15" t="n"/>
       <c r="G53" s="6" t="n"/>
       <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -9747,6 +9958,9 @@
       <c r="F54" s="15" t="n"/>
       <c r="G54" s="6" t="n"/>
       <c r="H54" s="6" t="n"/>
+      <c r="I54" s="6" t="n"/>
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -9757,6 +9971,9 @@
       <c r="F55" s="15" t="n"/>
       <c r="G55" s="6" t="n"/>
       <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="n"/>
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -9767,6 +9984,9 @@
       <c r="F56" s="15" t="n"/>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="6" t="n"/>
+      <c r="I56" s="6" t="n"/>
+      <c r="J56" s="6" t="n"/>
+      <c r="K56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -9777,6 +9997,9 @@
       <c r="F57" s="15" t="n"/>
       <c r="G57" s="6" t="n"/>
       <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="n"/>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -9787,6 +10010,9 @@
       <c r="F58" s="15" t="n"/>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="n"/>
+      <c r="J58" s="6" t="n"/>
+      <c r="K58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -9797,6 +10023,9 @@
       <c r="F59" s="15" t="n"/>
       <c r="G59" s="6" t="n"/>
       <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="n"/>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="E60" s="17" t="n"/>
@@ -13563,7 +13792,7 @@
       <c r="F1000" s="17" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." type="list">
       <formula1>=Days</formula1>
     </dataValidation>
@@ -13574,6 +13803,9 @@
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Enter a date" error="Enter a date, for example 2026-12-12." type="date" operator="between">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2040,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." type="list">
+      <formula1>=Repeats</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13588,7 +13820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U1000"/>
+  <dimension ref="A1:W1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13612,6 +13844,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -13718,6 +13952,16 @@
       <c r="U1" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="V1" s="10" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="W1" s="10" t="inlineStr">
+        <is>
+          <t>Uniform color</t>
         </is>
       </c>
     </row>
@@ -13795,6 +14039,8 @@
           <t>Schedules post the Wednesday before.</t>
         </is>
       </c>
+      <c r="V2" s="11" t="inlineStr"/>
+      <c r="W2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -13818,6 +14064,8 @@
       <c r="S3" s="6" t="n"/>
       <c r="T3" s="15" t="n"/>
       <c r="U3" s="6" t="n"/>
+      <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -13841,6 +14089,8 @@
       <c r="S4" s="6" t="n"/>
       <c r="T4" s="15" t="n"/>
       <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -13864,6 +14114,8 @@
       <c r="S5" s="6" t="n"/>
       <c r="T5" s="15" t="n"/>
       <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -13887,6 +14139,8 @@
       <c r="S6" s="6" t="n"/>
       <c r="T6" s="15" t="n"/>
       <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -13910,6 +14164,8 @@
       <c r="S7" s="6" t="n"/>
       <c r="T7" s="15" t="n"/>
       <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -13933,6 +14189,8 @@
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="15" t="n"/>
       <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -13956,6 +14214,8 @@
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="15" t="n"/>
       <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -13979,6 +14239,8 @@
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="15" t="n"/>
       <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -14002,6 +14264,8 @@
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="15" t="n"/>
       <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -14025,6 +14289,8 @@
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="15" t="n"/>
       <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -14048,6 +14314,8 @@
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="15" t="n"/>
       <c r="U13" s="6" t="n"/>
+      <c r="V13" s="6" t="n"/>
+      <c r="W13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -14071,6 +14339,8 @@
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="15" t="n"/>
       <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -14094,6 +14364,8 @@
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="15" t="n"/>
       <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -14117,6 +14389,8 @@
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="15" t="n"/>
       <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -14140,6 +14414,8 @@
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="15" t="n"/>
       <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -14163,6 +14439,8 @@
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="15" t="n"/>
       <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -14186,6 +14464,8 @@
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="15" t="n"/>
       <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -14209,6 +14489,8 @@
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="15" t="n"/>
       <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -14232,6 +14514,8 @@
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="15" t="n"/>
       <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -14255,6 +14539,8 @@
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="15" t="n"/>
       <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -14278,6 +14564,8 @@
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="15" t="n"/>
       <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -14301,6 +14589,8 @@
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="15" t="n"/>
       <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -14324,6 +14614,8 @@
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="15" t="n"/>
       <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -14347,6 +14639,8 @@
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="15" t="n"/>
       <c r="U26" s="6" t="n"/>
+      <c r="V26" s="6" t="n"/>
+      <c r="W26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -14370,6 +14664,8 @@
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="15" t="n"/>
       <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -14393,6 +14689,8 @@
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="15" t="n"/>
       <c r="U28" s="6" t="n"/>
+      <c r="V28" s="6" t="n"/>
+      <c r="W28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -14416,6 +14714,8 @@
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="15" t="n"/>
       <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -14439,6 +14739,8 @@
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="15" t="n"/>
       <c r="U30" s="6" t="n"/>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -14462,6 +14764,8 @@
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="15" t="n"/>
       <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -14485,6 +14789,8 @@
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="15" t="n"/>
       <c r="U32" s="6" t="n"/>
+      <c r="V32" s="6" t="n"/>
+      <c r="W32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -14508,6 +14814,8 @@
       <c r="S33" s="6" t="n"/>
       <c r="T33" s="15" t="n"/>
       <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -14531,6 +14839,8 @@
       <c r="S34" s="6" t="n"/>
       <c r="T34" s="15" t="n"/>
       <c r="U34" s="6" t="n"/>
+      <c r="V34" s="6" t="n"/>
+      <c r="W34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -14554,6 +14864,8 @@
       <c r="S35" s="6" t="n"/>
       <c r="T35" s="15" t="n"/>
       <c r="U35" s="6" t="n"/>
+      <c r="V35" s="6" t="n"/>
+      <c r="W35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -14577,6 +14889,8 @@
       <c r="S36" s="6" t="n"/>
       <c r="T36" s="15" t="n"/>
       <c r="U36" s="6" t="n"/>
+      <c r="V36" s="6" t="n"/>
+      <c r="W36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -14600,6 +14914,8 @@
       <c r="S37" s="6" t="n"/>
       <c r="T37" s="15" t="n"/>
       <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -14623,6 +14939,8 @@
       <c r="S38" s="6" t="n"/>
       <c r="T38" s="15" t="n"/>
       <c r="U38" s="6" t="n"/>
+      <c r="V38" s="6" t="n"/>
+      <c r="W38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -14646,6 +14964,8 @@
       <c r="S39" s="6" t="n"/>
       <c r="T39" s="15" t="n"/>
       <c r="U39" s="6" t="n"/>
+      <c r="V39" s="6" t="n"/>
+      <c r="W39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -14669,6 +14989,8 @@
       <c r="S40" s="6" t="n"/>
       <c r="T40" s="15" t="n"/>
       <c r="U40" s="6" t="n"/>
+      <c r="V40" s="6" t="n"/>
+      <c r="W40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -14692,6 +15014,8 @@
       <c r="S41" s="6" t="n"/>
       <c r="T41" s="15" t="n"/>
       <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -14715,6 +15039,8 @@
       <c r="S42" s="6" t="n"/>
       <c r="T42" s="15" t="n"/>
       <c r="U42" s="6" t="n"/>
+      <c r="V42" s="6" t="n"/>
+      <c r="W42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -14738,6 +15064,8 @@
       <c r="S43" s="6" t="n"/>
       <c r="T43" s="15" t="n"/>
       <c r="U43" s="6" t="n"/>
+      <c r="V43" s="6" t="n"/>
+      <c r="W43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -14761,6 +15089,8 @@
       <c r="S44" s="6" t="n"/>
       <c r="T44" s="15" t="n"/>
       <c r="U44" s="6" t="n"/>
+      <c r="V44" s="6" t="n"/>
+      <c r="W44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -14784,6 +15114,8 @@
       <c r="S45" s="6" t="n"/>
       <c r="T45" s="15" t="n"/>
       <c r="U45" s="6" t="n"/>
+      <c r="V45" s="6" t="n"/>
+      <c r="W45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -14807,6 +15139,8 @@
       <c r="S46" s="6" t="n"/>
       <c r="T46" s="15" t="n"/>
       <c r="U46" s="6" t="n"/>
+      <c r="V46" s="6" t="n"/>
+      <c r="W46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -14830,6 +15164,8 @@
       <c r="S47" s="6" t="n"/>
       <c r="T47" s="15" t="n"/>
       <c r="U47" s="6" t="n"/>
+      <c r="V47" s="6" t="n"/>
+      <c r="W47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -14853,6 +15189,8 @@
       <c r="S48" s="6" t="n"/>
       <c r="T48" s="15" t="n"/>
       <c r="U48" s="6" t="n"/>
+      <c r="V48" s="6" t="n"/>
+      <c r="W48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -14876,6 +15214,8 @@
       <c r="S49" s="6" t="n"/>
       <c r="T49" s="15" t="n"/>
       <c r="U49" s="6" t="n"/>
+      <c r="V49" s="6" t="n"/>
+      <c r="W49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -14899,6 +15239,8 @@
       <c r="S50" s="6" t="n"/>
       <c r="T50" s="15" t="n"/>
       <c r="U50" s="6" t="n"/>
+      <c r="V50" s="6" t="n"/>
+      <c r="W50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -14922,6 +15264,8 @@
       <c r="S51" s="6" t="n"/>
       <c r="T51" s="15" t="n"/>
       <c r="U51" s="6" t="n"/>
+      <c r="V51" s="6" t="n"/>
+      <c r="W51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -14945,6 +15289,8 @@
       <c r="S52" s="6" t="n"/>
       <c r="T52" s="15" t="n"/>
       <c r="U52" s="6" t="n"/>
+      <c r="V52" s="6" t="n"/>
+      <c r="W52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -14968,6 +15314,8 @@
       <c r="S53" s="6" t="n"/>
       <c r="T53" s="15" t="n"/>
       <c r="U53" s="6" t="n"/>
+      <c r="V53" s="6" t="n"/>
+      <c r="W53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -14991,6 +15339,8 @@
       <c r="S54" s="6" t="n"/>
       <c r="T54" s="15" t="n"/>
       <c r="U54" s="6" t="n"/>
+      <c r="V54" s="6" t="n"/>
+      <c r="W54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -15014,6 +15364,8 @@
       <c r="S55" s="6" t="n"/>
       <c r="T55" s="15" t="n"/>
       <c r="U55" s="6" t="n"/>
+      <c r="V55" s="6" t="n"/>
+      <c r="W55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -15037,6 +15389,8 @@
       <c r="S56" s="6" t="n"/>
       <c r="T56" s="15" t="n"/>
       <c r="U56" s="6" t="n"/>
+      <c r="V56" s="6" t="n"/>
+      <c r="W56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -15060,6 +15414,8 @@
       <c r="S57" s="6" t="n"/>
       <c r="T57" s="15" t="n"/>
       <c r="U57" s="6" t="n"/>
+      <c r="V57" s="6" t="n"/>
+      <c r="W57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -15083,6 +15439,8 @@
       <c r="S58" s="6" t="n"/>
       <c r="T58" s="15" t="n"/>
       <c r="U58" s="6" t="n"/>
+      <c r="V58" s="6" t="n"/>
+      <c r="W58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -15106,6 +15464,8 @@
       <c r="S59" s="6" t="n"/>
       <c r="T59" s="15" t="n"/>
       <c r="U59" s="6" t="n"/>
+      <c r="V59" s="6" t="n"/>
+      <c r="W59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="C60" s="17" t="n"/>
@@ -21132,7 +21492,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Tournament</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -21179,7 +21539,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Tournament</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -21221,7 +21581,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -21232,6 +21592,11 @@
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Youth L</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -21251,6 +21616,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Every 3 weeks</t>
@@ -21259,6 +21629,11 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Youth XL</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
         </is>
       </c>
     </row>

--- a/web/public/templates/Team-Setup-Template.xlsx
+++ b/web/public/templates/Team-Setup-Template.xlsx
@@ -386,6 +386,11 @@
         <t>Practice uniform color. New colors are added to the team's list.</t>
       </text>
     </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Street address. Families get a map link; without one the map searches the location.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -434,6 +439,16 @@
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>Practices only.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Street address of the venue. Families get a map link; without one the map searches the venue and city.</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>Travel tournaments: the team hotel's street address.</t>
       </text>
     </comment>
   </commentList>
@@ -9160,7 +9175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9174,6 +9189,7 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -9232,6 +9248,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -9283,6 +9304,11 @@
       <c r="K2" s="11" t="inlineStr">
         <is>
           <t>Bring both jerseys</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>1234 Example Rd, Roswell, GA 30076</t>
         </is>
       </c>
     </row>
@@ -9298,6 +9324,7 @@
       <c r="I3" s="6" t="n"/>
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -9311,6 +9338,7 @@
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -9324,6 +9352,7 @@
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -9337,6 +9366,7 @@
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -9350,6 +9380,7 @@
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -9363,6 +9394,7 @@
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -9376,6 +9408,7 @@
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -9389,6 +9422,7 @@
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -9402,6 +9436,7 @@
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -9415,6 +9450,7 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -9428,6 +9464,7 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -9441,6 +9478,7 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -9454,6 +9492,7 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -9467,6 +9506,7 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9480,6 +9520,7 @@
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -9493,6 +9534,7 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -9506,6 +9548,7 @@
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -9519,6 +9562,7 @@
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9532,6 +9576,7 @@
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -9545,6 +9590,7 @@
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -9558,6 +9604,7 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -9571,6 +9618,7 @@
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -9584,6 +9632,7 @@
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -9597,6 +9646,7 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -9610,6 +9660,7 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -9623,6 +9674,7 @@
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -9636,6 +9688,7 @@
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -9649,6 +9702,7 @@
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -9662,6 +9716,7 @@
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -9675,6 +9730,7 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -9688,6 +9744,7 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -9701,6 +9758,7 @@
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -9714,6 +9772,7 @@
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -9727,6 +9786,7 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -9740,6 +9800,7 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -9753,6 +9814,7 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -9766,6 +9828,7 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -9779,6 +9842,7 @@
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -9792,6 +9856,7 @@
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -9805,6 +9870,7 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -9818,6 +9884,7 @@
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -9831,6 +9898,7 @@
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -9844,6 +9912,7 @@
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -9857,6 +9926,7 @@
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -9870,6 +9940,7 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -9883,6 +9954,7 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -9896,6 +9968,7 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -9909,6 +9982,7 @@
       <c r="I50" s="6" t="n"/>
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -9922,6 +9996,7 @@
       <c r="I51" s="6" t="n"/>
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -9935,6 +10010,7 @@
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -9948,6 +10024,7 @@
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -9961,6 +10038,7 @@
       <c r="I54" s="6" t="n"/>
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -9974,6 +10052,7 @@
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -9987,6 +10066,7 @@
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -10000,6 +10080,7 @@
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -10013,6 +10094,7 @@
       <c r="I58" s="6" t="n"/>
       <c r="J58" s="6" t="n"/>
       <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -10026,6 +10108,7 @@
       <c r="I59" s="6" t="n"/>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="E60" s="17" t="n"/>
@@ -13820,7 +13903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W1000"/>
+  <dimension ref="A1:Y1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13846,6 +13929,8 @@
     <col width="36" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -13962,6 +14047,16 @@
       <c r="W1" s="10" t="inlineStr">
         <is>
           <t>Uniform color</t>
+        </is>
+      </c>
+      <c r="X1" s="10" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="Y1" s="10" t="inlineStr">
+        <is>
+          <t>Hotel address</t>
         </is>
       </c>
     </row>
@@ -14041,6 +14136,12 @@
       </c>
       <c r="V2" s="11" t="inlineStr"/>
       <c r="W2" s="11" t="inlineStr"/>
+      <c r="X2" s="11" t="inlineStr">
+        <is>
+          <t>285 Andrew Young International Blvd NW, Atlanta, GA 30313</t>
+        </is>
+      </c>
+      <c r="Y2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -14066,6 +14167,8 @@
       <c r="U3" s="6" t="n"/>
       <c r="V3" s="6" t="n"/>
       <c r="W3" s="6" t="n"/>
+      <c r="X3" s="6" t="n"/>
+      <c r="Y3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -14091,6 +14194,8 @@
       <c r="U4" s="6" t="n"/>
       <c r="V4" s="6" t="n"/>
       <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -14116,6 +14221,8 @@
       <c r="U5" s="6" t="n"/>
       <c r="V5" s="6" t="n"/>
       <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -14141,6 +14248,8 @@
       <c r="U6" s="6" t="n"/>
       <c r="V6" s="6" t="n"/>
       <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -14166,6 +14275,8 @@
       <c r="U7" s="6" t="n"/>
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -14191,6 +14302,8 @@
       <c r="U8" s="6" t="n"/>
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -14216,6 +14329,8 @@
       <c r="U9" s="6" t="n"/>
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -14241,6 +14356,8 @@
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -14266,6 +14383,8 @@
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -14291,6 +14410,8 @@
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -14316,6 +14437,8 @@
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -14341,6 +14464,8 @@
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -14366,6 +14491,8 @@
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -14391,6 +14518,8 @@
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -14416,6 +14545,8 @@
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -14441,6 +14572,8 @@
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -14466,6 +14599,8 @@
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -14491,6 +14626,8 @@
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -14516,6 +14653,8 @@
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -14541,6 +14680,8 @@
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -14566,6 +14707,8 @@
       <c r="U23" s="6" t="n"/>
       <c r="V23" s="6" t="n"/>
       <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -14591,6 +14734,8 @@
       <c r="U24" s="6" t="n"/>
       <c r="V24" s="6" t="n"/>
       <c r="W24" s="6" t="n"/>
+      <c r="X24" s="6" t="n"/>
+      <c r="Y24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -14616,6 +14761,8 @@
       <c r="U25" s="6" t="n"/>
       <c r="V25" s="6" t="n"/>
       <c r="W25" s="6" t="n"/>
+      <c r="X25" s="6" t="n"/>
+      <c r="Y25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -14641,6 +14788,8 @@
       <c r="U26" s="6" t="n"/>
       <c r="V26" s="6" t="n"/>
       <c r="W26" s="6" t="n"/>
+      <c r="X26" s="6" t="n"/>
+      <c r="Y26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -14666,6 +14815,8 @@
       <c r="U27" s="6" t="n"/>
       <c r="V27" s="6" t="n"/>
       <c r="W27" s="6" t="n"/>
+      <c r="X27" s="6" t="n"/>
+      <c r="Y27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -14691,6 +14842,8 @@
       <c r="U28" s="6" t="n"/>
       <c r="V28" s="6" t="n"/>
       <c r="W28" s="6" t="n"/>
+      <c r="X28" s="6" t="n"/>
+      <c r="Y28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -14716,6 +14869,8 @@
       <c r="U29" s="6" t="n"/>
       <c r="V29" s="6" t="n"/>
       <c r="W29" s="6" t="n"/>
+      <c r="X29" s="6" t="n"/>
+      <c r="Y29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -14741,6 +14896,8 @@
       <c r="U30" s="6" t="n"/>
       <c r="V30" s="6" t="n"/>
       <c r="W30" s="6" t="n"/>
+      <c r="X30" s="6" t="n"/>
+      <c r="Y30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -14766,6 +14923,8 @@
       <c r="U31" s="6" t="n"/>
       <c r="V31" s="6" t="n"/>
       <c r="W31" s="6" t="n"/>
+      <c r="X31" s="6" t="n"/>
+      <c r="Y31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -14791,6 +14950,8 @@
       <c r="U32" s="6" t="n"/>
       <c r="V32" s="6" t="n"/>
       <c r="W32" s="6" t="n"/>
+      <c r="X32" s="6" t="n"/>
+      <c r="Y32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -14816,6 +14977,8 @@
       <c r="U33" s="6" t="n"/>
       <c r="V33" s="6" t="n"/>
       <c r="W33" s="6" t="n"/>
+      <c r="X33" s="6" t="n"/>
+      <c r="Y33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -14841,6 +15004,8 @@
       <c r="U34" s="6" t="n"/>
       <c r="V34" s="6" t="n"/>
       <c r="W34" s="6" t="n"/>
+      <c r="X34" s="6" t="n"/>
+      <c r="Y34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -14866,6 +15031,8 @@
       <c r="U35" s="6" t="n"/>
       <c r="V35" s="6" t="n"/>
       <c r="W35" s="6" t="n"/>
+      <c r="X35" s="6" t="n"/>
+      <c r="Y35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -14891,6 +15058,8 @@
       <c r="U36" s="6" t="n"/>
       <c r="V36" s="6" t="n"/>
       <c r="W36" s="6" t="n"/>
+      <c r="X36" s="6" t="n"/>
+      <c r="Y36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -14916,6 +15085,8 @@
       <c r="U37" s="6" t="n"/>
       <c r="V37" s="6" t="n"/>
       <c r="W37" s="6" t="n"/>
+      <c r="X37" s="6" t="n"/>
+      <c r="Y37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -14941,6 +15112,8 @@
       <c r="U38" s="6" t="n"/>
       <c r="V38" s="6" t="n"/>
       <c r="W38" s="6" t="n"/>
+      <c r="X38" s="6" t="n"/>
+      <c r="Y38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -14966,6 +15139,8 @@
       <c r="U39" s="6" t="n"/>
       <c r="V39" s="6" t="n"/>
       <c r="W39" s="6" t="n"/>
+      <c r="X39" s="6" t="n"/>
+      <c r="Y39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -14991,6 +15166,8 @@
       <c r="U40" s="6" t="n"/>
       <c r="V40" s="6" t="n"/>
       <c r="W40" s="6" t="n"/>
+      <c r="X40" s="6" t="n"/>
+      <c r="Y40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -15016,6 +15193,8 @@
       <c r="U41" s="6" t="n"/>
       <c r="V41" s="6" t="n"/>
       <c r="W41" s="6" t="n"/>
+      <c r="X41" s="6" t="n"/>
+      <c r="Y41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -15041,6 +15220,8 @@
       <c r="U42" s="6" t="n"/>
       <c r="V42" s="6" t="n"/>
       <c r="W42" s="6" t="n"/>
+      <c r="X42" s="6" t="n"/>
+      <c r="Y42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -15066,6 +15247,8 @@
       <c r="U43" s="6" t="n"/>
       <c r="V43" s="6" t="n"/>
       <c r="W43" s="6" t="n"/>
+      <c r="X43" s="6" t="n"/>
+      <c r="Y43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -15091,6 +15274,8 @@
       <c r="U44" s="6" t="n"/>
       <c r="V44" s="6" t="n"/>
       <c r="W44" s="6" t="n"/>
+      <c r="X44" s="6" t="n"/>
+      <c r="Y44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -15116,6 +15301,8 @@
       <c r="U45" s="6" t="n"/>
       <c r="V45" s="6" t="n"/>
       <c r="W45" s="6" t="n"/>
+      <c r="X45" s="6" t="n"/>
+      <c r="Y45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -15141,6 +15328,8 @@
       <c r="U46" s="6" t="n"/>
       <c r="V46" s="6" t="n"/>
       <c r="W46" s="6" t="n"/>
+      <c r="X46" s="6" t="n"/>
+      <c r="Y46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -15166,6 +15355,8 @@
       <c r="U47" s="6" t="n"/>
       <c r="V47" s="6" t="n"/>
       <c r="W47" s="6" t="n"/>
+      <c r="X47" s="6" t="n"/>
+      <c r="Y47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -15191,6 +15382,8 @@
       <c r="U48" s="6" t="n"/>
       <c r="V48" s="6" t="n"/>
       <c r="W48" s="6" t="n"/>
+      <c r="X48" s="6" t="n"/>
+      <c r="Y48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -15216,6 +15409,8 @@
       <c r="U49" s="6" t="n"/>
       <c r="V49" s="6" t="n"/>
       <c r="W49" s="6" t="n"/>
+      <c r="X49" s="6" t="n"/>
+      <c r="Y49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -15241,6 +15436,8 @@
       <c r="U50" s="6" t="n"/>
       <c r="V50" s="6" t="n"/>
       <c r="W50" s="6" t="n"/>
+      <c r="X50" s="6" t="n"/>
+      <c r="Y50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -15266,6 +15463,8 @@
       <c r="U51" s="6" t="n"/>
       <c r="V51" s="6" t="n"/>
       <c r="W51" s="6" t="n"/>
+      <c r="X51" s="6" t="n"/>
+      <c r="Y51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -15291,6 +15490,8 @@
       <c r="U52" s="6" t="n"/>
       <c r="V52" s="6" t="n"/>
       <c r="W52" s="6" t="n"/>
+      <c r="X52" s="6" t="n"/>
+      <c r="Y52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -15316,6 +15517,8 @@
       <c r="U53" s="6" t="n"/>
       <c r="V53" s="6" t="n"/>
       <c r="W53" s="6" t="n"/>
+      <c r="X53" s="6" t="n"/>
+      <c r="Y53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -15341,6 +15544,8 @@
       <c r="U54" s="6" t="n"/>
       <c r="V54" s="6" t="n"/>
       <c r="W54" s="6" t="n"/>
+      <c r="X54" s="6" t="n"/>
+      <c r="Y54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -15366,6 +15571,8 @@
       <c r="U55" s="6" t="n"/>
       <c r="V55" s="6" t="n"/>
       <c r="W55" s="6" t="n"/>
+      <c r="X55" s="6" t="n"/>
+      <c r="Y55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -15391,6 +15598,8 @@
       <c r="U56" s="6" t="n"/>
       <c r="V56" s="6" t="n"/>
       <c r="W56" s="6" t="n"/>
+      <c r="X56" s="6" t="n"/>
+      <c r="Y56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -15416,6 +15625,8 @@
       <c r="U57" s="6" t="n"/>
       <c r="V57" s="6" t="n"/>
       <c r="W57" s="6" t="n"/>
+      <c r="X57" s="6" t="n"/>
+      <c r="Y57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -15441,6 +15652,8 @@
       <c r="U58" s="6" t="n"/>
       <c r="V58" s="6" t="n"/>
       <c r="W58" s="6" t="n"/>
+      <c r="X58" s="6" t="n"/>
+      <c r="Y58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -15466,6 +15679,8 @@
       <c r="U59" s="6" t="n"/>
       <c r="V59" s="6" t="n"/>
       <c r="W59" s="6" t="n"/>
+      <c r="X59" s="6" t="n"/>
+      <c r="Y59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="C60" s="17" t="n"/>

--- a/web/public/templates/Team-Setup-Template.xlsx
+++ b/web/public/templates/Team-Setup-Template.xlsx
@@ -23,7 +23,7 @@
     <definedName name="Repeats">Choices!$D$2:$D$5</definedName>
     <definedName name="Shirts">Choices!$E$2:$E$11</definedName>
     <definedName name="RefGroups">Choices!$F$2:$F$3</definedName>
-    <definedName name="Lists">Choices!$G$2:$G$4</definedName>
+    <definedName name="Lists">Choices!$G$2:$G$5</definedName>
     <definedName name="Programs">Choices!$H$2:$H$4</definedName>
     <definedName name="DefaultKinds">Choices!$I$2:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Team'!$1:$1</definedName>
@@ -233,7 +233,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -273,7 +273,7 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -308,7 +308,7 @@
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -358,7 +358,7 @@
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -398,7 +398,7 @@
 <file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Team Hub</author>
+    <author>Teem Hub</author>
   </authors>
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -449,6 +449,26 @@
     <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>Travel tournaments: the team hotel's street address.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Teem Hub</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>The item, or for a handbook section its text.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>For handbook sections.</t>
       </text>
     </comment>
   </commentList>
@@ -762,7 +782,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fill in this workbook to set up one team in Team Hub: who's on it, its staff and practices, and its season schedule. Club admins upload it from the team's Members page, or from the club page to create a new team.</t>
+          <t>Fill in this workbook to set up one team in Teem Hub: who's on it, its staff and practices, and its season schedule. Club admins upload it from the team's Members page, or from the club page to create a new team.</t>
         </is>
       </c>
     </row>
@@ -957,11 +977,11 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Optional: packing checklist, uniform items and practice uniform colors.</t>
+          <t>Optional: packing checklist, uniform items, practice uniform colors and handbook sections.</t>
         </is>
       </c>
       <c r="C19" s="6">
-        <f>COUNTA(Lists!B3:B1000)</f>
+        <f>COUNTA(Lists!A3:A1000)</f>
         <v/>
       </c>
     </row>
@@ -1016,7 +1036,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Each person marked for an invite gets the right role, linked to their player, as soon as they sign in or create an account with that email. Team Hub doesn't email them yet, so let them know.</t>
+          <t>Each person marked for an invite gets the right role, linked to their player, as soon as they sign in or create an account with that email. Teem Hub doesn't email them yet, so let them know.</t>
         </is>
       </c>
     </row>
@@ -21368,11 +21388,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -21386,6 +21407,11 @@
           <t>Item *</t>
         </is>
       </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -21398,234 +21424,292 @@
           <t>Knee and elbow pads</t>
         </is>
       </c>
+      <c r="C2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
       <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
       <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -21635,6 +21719,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -21846,6 +21931,11 @@
           <t>Youth XL</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Handbook section</t>
+        </is>
+      </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Practice uniform colors</t>

--- a/web/public/templates/Team-Setup-Template.xlsx
+++ b/web/public/templates/Team-Setup-Template.xlsx
@@ -475,6 +475,36 @@
 </comments>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="495300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -764,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A2:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -772,235 +802,224 @@
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="44" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Team setup</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Fill in this workbook to set up one team in Teem Hub: who's on it, its staff and practices, and its season schedule. Club admins upload it from the team's Members page, or from the club page to create a new team.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>How to fill it in</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Red header *</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Required column. Rows missing it are listed as problems in the upload preview.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Navy header</t>
+          <t>Red header *</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Optional column.</t>
+          <t>Required column. Rows missing it are listed as problems in the upload preview.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Grey italic row 2</t>
+          <t>Navy header</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>An example showing the format. Type over it or delete it; it is skipped if left unchanged.</t>
+          <t>Optional column.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Dropdown cells</t>
+          <t>Grey italic row 2</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Pick from the list. Hover over a header for a note on that column.</t>
+          <t>An example showing the format. Type over it or delete it; it is skipped if left unchanged.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Dropdown cells</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Any Excel date, or text like 2026-12-12.</t>
+          <t>Pick from the list. Hover over a header for a note on that column.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Times</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Text like 6:30 PM.</t>
+          <t>Any Excel date, or text like 2026-12-12.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>Times</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Text like 6:30 PM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Leave out</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Availability, travel plans, uniform sizes, meal claims and payments: families enter these themselves. Never add passwords.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Tabs</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Rows filled</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>One row: the team's name, season and fund settings.</t>
         </is>
       </c>
-      <c r="C14" s="6">
+      <c r="C15" s="6">
         <f>COUNTA(Team!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>One row per coach, coordinator or other staff member.</t>
         </is>
       </c>
-      <c r="C15" s="6">
+      <c r="C16" s="6">
         <f>COUNTA(Staff!C3:C1000)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Roster</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>One row per player, with up to four parents.</t>
         </is>
       </c>
-      <c r="C16" s="6">
+      <c r="C17" s="6">
         <f>COUNTA(Roster!B3:B1000)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Practices</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>One row per practice series: weekly, every 2 weeks or every 3 weeks.</t>
         </is>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <f>COUNTA(Practices!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>One row per tournament, team event, deadline or one-off practice.</t>
         </is>
       </c>
-      <c r="C18" s="6">
+      <c r="C19" s="6">
         <f>COUNTA(Schedule!B3:B1000)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Lists</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Optional: packing checklist, uniform items, practice uniform colors and handbook sections.</t>
         </is>
       </c>
-      <c r="C19" s="6">
+      <c r="C20" s="6">
         <f>COUNTA(Lists!A3:A1000)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>When you upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>You see a preview first: what will be created, and each problem by tab and row. Nothing is saved until you confirm.</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1031,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Uploading again updates what's there instead of adding duplicates. Teams match on Team ID, players on jersey or name, events on type, date and title, people on email. Blank cells keep what's saved.</t>
+          <t>You see a preview first: what will be created, and each problem by tab and row. Nothing is saved until you confirm.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1043,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Nothing is removed: players, events and people already on a team but not in the workbook stay, and so do answers, payments and travel plans families entered.</t>
+          <t>Uploading again updates what's there instead of adding duplicates. Teams match on Team ID, players on jersey or name, events on type, date and title, people on email. Blank cells keep what's saved.</t>
         </is>
       </c>
     </row>
@@ -1036,16 +1055,29 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
+          <t>Nothing is removed: players, events and people already on a team but not in the workbook stay, and so do answers, payments and travel plans families entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
           <t>Each person marked for an invite gets the right role, linked to their player, as soon as they sign in or create an account with that email. Teem Hub doesn't email them yet, so let them know.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
